--- a/files/九龙-长沙湾-幸荟.xlsx
+++ b/files/九龙-长沙湾-幸荟.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸荟 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="幸荟" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,19 +213,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,10 +231,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5059,127 +5097,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>幸荟 - 幸荟 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>幸荟 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>95 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>92 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 招标单位
@@ -5187,7 +5225,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $398万
@@ -5195,7 +5233,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $389万
@@ -5203,7 +5241,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 招标单位
@@ -5211,7 +5249,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 招标单位
@@ -5220,13 +5258,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $446万
@@ -5234,7 +5272,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $356万
@@ -5242,7 +5280,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $349万
@@ -5250,7 +5288,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $606万
@@ -5258,7 +5296,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $421万
@@ -5267,13 +5305,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $433万
@@ -5281,7 +5319,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $353万
@@ -5289,7 +5327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $346万
@@ -5297,7 +5335,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $602万
@@ -5305,7 +5343,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $412万
@@ -5314,13 +5352,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $430万
@@ -5328,7 +5366,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $351万
@@ -5336,7 +5374,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $343万
@@ -5344,7 +5382,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $610万
@@ -5352,7 +5390,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $408万
@@ -5361,13 +5399,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $426万
@@ -5375,7 +5413,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $348万
@@ -5383,7 +5421,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $341万
@@ -5391,7 +5429,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $592万
@@ -5399,7 +5437,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $405万
@@ -5408,13 +5446,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $421万
@@ -5422,7 +5460,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $344万
@@ -5430,7 +5468,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $336万
@@ -5438,7 +5476,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $585万
@@ -5446,7 +5484,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $401万
@@ -5455,13 +5493,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $416万
@@ -5469,7 +5507,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $339万
@@ -5477,7 +5515,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $332万
@@ -5485,7 +5523,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $577万
@@ -5493,7 +5531,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $396万
@@ -5502,13 +5540,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $411万
@@ -5516,7 +5554,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $335万
@@ -5524,7 +5562,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $328万
@@ -5532,7 +5570,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $570万
@@ -5540,7 +5578,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $391万
@@ -5549,13 +5587,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $406万
@@ -5563,7 +5601,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $331万
@@ -5571,7 +5609,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $324万
@@ -5579,7 +5617,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $563万
@@ -5587,7 +5625,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $386万
@@ -5596,13 +5634,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $401万
@@ -5610,7 +5648,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $327万
@@ -5618,7 +5656,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $320万
@@ -5626,7 +5664,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $556万
@@ -5634,7 +5672,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $379万
@@ -5643,13 +5681,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $395万
@@ -5657,7 +5695,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $323万
@@ -5665,7 +5703,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $316万
@@ -5673,7 +5711,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $549万
@@ -5681,7 +5719,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $374万
@@ -5690,13 +5728,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $390万
@@ -5704,7 +5742,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $326万
@@ -5712,7 +5750,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $312万
@@ -5720,7 +5758,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $542万
@@ -5728,7 +5766,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $369万
@@ -5737,13 +5775,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $385万
@@ -5751,7 +5789,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $315万
@@ -5759,7 +5797,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $308万
@@ -5767,7 +5805,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $536万
@@ -5775,7 +5813,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $365万
@@ -5784,13 +5822,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $380万
@@ -5798,7 +5836,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $311万
@@ -5806,7 +5844,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $304万
@@ -5814,7 +5852,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $529万
@@ -5822,7 +5860,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $360万
@@ -5831,13 +5869,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $374万
@@ -5845,7 +5883,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $306万
@@ -5853,7 +5891,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $300万
@@ -5861,7 +5899,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $521万
@@ -5869,7 +5907,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $354万
@@ -5878,13 +5916,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $371万
@@ -5892,7 +5930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $303万
@@ -5900,7 +5938,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $297万
@@ -5908,7 +5946,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $515万
@@ -5916,7 +5954,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $350万
@@ -5925,13 +5963,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $362万
@@ -5939,7 +5977,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $298万
@@ -5947,7 +5985,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $292万
@@ -5955,7 +5993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $507万
@@ -5963,7 +6001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $345万
@@ -5972,13 +6010,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 237呎 (开放式)
 $354万
@@ -5986,7 +6024,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 181呎 (开放式)
 $304万
@@ -5994,7 +6032,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $288万
@@ -6002,7 +6040,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 309呎 (2房)
 $500万
@@ -6010,7 +6048,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 223呎 (开放式)
 $341万
@@ -6019,13 +6057,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 200呎 (开放式)
 $370万
@@ -6033,7 +6071,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 144呎 (开放式)
 $302万
@@ -6041,7 +6079,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 135呎 (开放式)
 $289万
@@ -6049,7 +6087,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 272呎 (2房)
 $530万
@@ -6057,7 +6095,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 185呎 (开放式)
 $430万
